--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/accounadjustmanage/taxflowquery/TaxFlowQuery001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/accounadjustmanage/taxflowquery/TaxFlowQuery001.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SVN本地代码\2.1.2\tams-valuation-parent\tams-valuation\src\main\resources\tpl\accounadjustmanage\taxflowquery\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2715" windowWidth="13050" windowHeight="6135"/>
+    <workbookView xWindow="0" yWindow="2712" windowWidth="13056" windowHeight="6132"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,10 +56,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>应税税率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>含税销售额本币</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -74,6 +65,10 @@
   </si>
   <si>
     <t>销售额本币</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>应税税率(%)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -183,7 +178,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -225,7 +220,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -260,7 +255,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -470,24 +465,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.75" style="1" customWidth="1"/>
+    <col min="1" max="2" width="18.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="25" style="1" customWidth="1"/>
-    <col min="4" max="5" width="13.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="13.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="1" customWidth="1"/>
     <col min="10" max="11" width="14" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.25" style="1" customWidth="1"/>
-    <col min="13" max="14" width="16.125" style="2" customWidth="1"/>
-    <col min="15" max="16" width="21.25" style="2" customWidth="1"/>
-    <col min="17" max="17" width="16.125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.21875" style="1" customWidth="1"/>
+    <col min="13" max="14" width="16.109375" style="2" customWidth="1"/>
+    <col min="15" max="16" width="21.21875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="16.109375" style="2" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -519,7 +514,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>10</v>
@@ -528,16 +523,16 @@
         <v>11</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
